--- a/QA_테스트_결과보고서.xlsx
+++ b/QA_테스트_결과보고서.xlsx
@@ -1505,7 +1505,7 @@
       </c>
       <c r="K5" s="15" t="inlineStr">
         <is>
-          <t>200 · GL3,HO2 · 871ms</t>
+          <t>200 · GL3,HO2 · 531ms</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>871ms (콜드스타트 최초 1회는 3115ms)</t>
+          <t>531ms (콜드스타트 최초 1회는 2320ms)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>결과=0건 · 유형="분류 미상"</t>
+          <t>결과=0건 · 유형="미보유 시설 · 수영장"</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>qa-1786589505598@test.modi</t>
+          <t>qa-1786592236522@test.modi</t>
         </is>
       </c>
       <c r="J20" s="17" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>HTTP 200 qa-1786589505598@test.modi</t>
+          <t>HTTP 200 qa-1786592236522@test.modi</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>HTTP 200 · REV-260813-1240</t>
+          <t>HTTP 200 · REV-260813-1609</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>HTTP 200 · REV-260813-3000</t>
+          <t>HTTP 200 · REV-260813-3229</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>HTTP 200 · REV-260813-5279</t>
+          <t>HTTP 200 · REV-260813-6726</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>DELETE REV-260813-1240</t>
+          <t>DELETE REV-260813-1609</t>
         </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>DELETE REV-260813-1240 (타인 소유)</t>
+          <t>DELETE REV-260813-1609 (타인 소유)</t>
         </is>
       </c>
       <c r="J36" s="17" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="K45" s="15" t="inlineStr">
         <is>
-          <t>검색 251건 · 미충족 164건</t>
+          <t>검색 144건 · 미충족 54건</t>
         </is>
       </c>
       <c r="L45" s="20" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="K46" s="17" t="inlineStr">
         <is>
-          <t>분류 미상(148), 영주 지역 회의·교육(8), 키친·조리(1), 부녀회 활동 공간(1), 요청 정보 불분명(1), 15명 이상 단체 조리 공간(1), 요청 유형 없음(1), 유효하지 않은 공간 검색 요청(1), 워밍업 공간(1), 수영장(1)</t>
+          <t>미보유 시설 · 수영장(20), 분류 미상(16), 영주 지역 회의·교육(10), 미보유 시설 · 체육시설(3), 키친·조리(2), 부녀회 활동 공간(1), 요청 정보 불분명(1), 15명 이상 단체 조리 공간(1)</t>
         </is>
       </c>
       <c r="L46" s="22" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>무LLM 96% · ③ 임베딩:156 ① 조건필터:68 ② 퍼지:18 ④ LLM:9</t>
+          <t>무LLM 97% · ① 조건필터:81 ③ 임베딩:39 ② 퍼지:20 ④ LLM:4</t>
         </is>
       </c>
       <c r="L47" s="20" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K49" s="15" t="inlineStr">
         <is>
-          <t>10건 · 시간이 안 맞아요</t>
+          <t>11건 · 시간이 안 맞아요</t>
         </is>
       </c>
       <c r="L49" s="20" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="K51" s="15" t="inlineStr">
         <is>
-          <t>총 4건 · 대기 1 · 취소 3</t>
+          <t>총 5건 · 대기 2 · 취소 3</t>
         </is>
       </c>
       <c r="L51" s="20" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>status=200 목록=1건 counts={"승인대기":1,"예약확정":0,"반려":0,"취소":3}</t>
+          <t>status=200 목록=2건 counts={"승인대기":2,"예약확정":0,"반려":0,"취소":3}</t>
         </is>
       </c>
       <c r="L67" s="20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>REV-260813-8725 승인대기</t>
+          <t>REV-260813-7695 승인대기</t>
         </is>
       </c>
       <c r="I69" s="15" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>REV-260813-8725 승인대기</t>
+          <t>REV-260813-7695 승인대기</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>REV-260813-8725 승인대기</t>
+          <t>REV-260813-7695 승인대기</t>
         </is>
       </c>
       <c r="I71" s="15" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>REV-260813-8725 예약확정</t>
+          <t>REV-260813-7695 예약확정</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>dist/assets/*.js (567KB)</t>
+          <t>dist/assets/*.js (568KB)</t>
         </is>
       </c>
       <c r="J80" s="17" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="K81" s="15" t="inlineStr">
         <is>
-          <t>25회 중 통과=19 차단=6 (17906ms)</t>
+          <t>25회 중 통과=19 차단=6 (16831ms)</t>
         </is>
       </c>
       <c r="L81" s="20" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>251</v>
+        <v>142</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="B6" s="32" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="B8" s="32" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>242</v>
+        <v>138</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="B10" s="32" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>747</v>
+        <v>618</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         </is>
       </c>
       <c r="B12" s="32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>155ms</t>
+          <t>98ms</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>[일일 한도 초과(429)]</t>
+          <t>GL4M,HO3</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>[일일 한도 초과(429)]</t>
+          <t>GL4</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>[일일 한도 초과(429)]</t>
+          <t>GL7</t>
         </is>
       </c>
     </row>
